--- a/v4/구매신청_최종.xlsx
+++ b/v4/구매신청_최종.xlsx
@@ -635,16 +635,16 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>가변저항 B10K</t>
+          <t>네오디뮴 자석</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>회전형 16mm, 축 Ø6 반달(D컷, 평면까지 4.5~4.6), 축 길이 15mm(장착면부터), 부싱 M7</t>
+          <t>Ø6×3mm</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>3993</v>
+        <v>220</v>
       </c>
       <c r="G7" s="6">
         <f>D7*F7</f>
@@ -665,7 +665,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>16130996</t>
+          <t>31671</t>
         </is>
       </c>
     </row>
@@ -675,16 +675,16 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>연마봉(강철 축)</t>
+          <t>가변저항 B10K</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Ø12 1m (435·358·160 으로 절단)</t>
+          <t>회전형 16mm, 축 Ø6 반달(D컷, 평면까지 4.5~4.6), 축 길이 15mm(장착면부터), 부싱 M7</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>16000</v>
+        <v>3993</v>
       </c>
       <c r="G8" s="6">
         <f>D8*F8</f>
@@ -700,10 +700,14 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>소망트레이딩</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr"/>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>16130996</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -711,12 +715,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>연마봉(강철 축) 짧은 것</t>
+          <t>만능기판</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Ø12, 55mm 이상 (55로 절단)</t>
+          <t>하프 사이즈 89×52 (브레드보드형, 양면)</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -724,11 +728,11 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>장</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1600</v>
+        <v>2420</v>
       </c>
       <c r="G9" s="6">
         <f>D9*F9</f>
@@ -736,10 +740,14 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>소망트레이딩</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr"/>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>12506669</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -747,16 +755,16 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>연마봉(변속 레일)</t>
+          <t>비상정지 스위치</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Ø6, 371mm</t>
+          <t>버섯형, b접점(NC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -764,7 +772,7 @@
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>5200</v>
+        <v>7370</v>
       </c>
       <c r="G10" s="6">
         <f>D10*F10</f>
@@ -772,10 +780,14 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>소망트레이딩</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr"/>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>10895020</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -783,24 +795,24 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>6001ZZ 볼 베어링 (10개 묶음)</t>
+          <t>5V 릴레이 모듈</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>12×28×8</t>
+          <t>1채널, 로우 트리거</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>묶음</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6000</v>
+        <v>990</v>
       </c>
       <c r="G11" s="6">
         <f>D11*F11</f>
@@ -808,12 +820,12 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>디바이스마트</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>8630678241</t>
+          <t>1327543</t>
         </is>
       </c>
     </row>
@@ -823,16 +835,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>6003ZZ 볼 베어링</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>17×35×10</t>
-        </is>
-      </c>
+          <t>다이오드 1N4007</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -840,7 +848,7 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1100</v>
+        <v>22</v>
       </c>
       <c r="G12" s="6">
         <f>D12*F12</f>
@@ -848,12 +856,12 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>디바이스마트</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>8230435105</t>
+          <t>3011</t>
         </is>
       </c>
     </row>
@@ -863,12 +871,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>강철 평행핀</t>
+          <t>저항</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Ø5×25</t>
+          <t>10kΩ 30개 + 4.7kΩ 30개 (1/4W, 최소 수량)</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -876,11 +884,11 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>봉(100개)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27000</v>
+        <v>1518</v>
       </c>
       <c r="G13" s="6">
         <f>D13*F13</f>
@@ -888,12 +896,12 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>디바이스마트</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>9743421687</t>
+          <t>856</t>
         </is>
       </c>
     </row>
@@ -903,16 +911,16 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>강철 평행핀</t>
+          <t>연마봉(강철 축)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Ø5×40</t>
+          <t>Ø12 1m (435·358·160 으로 절단)</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -920,7 +928,7 @@
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>440</v>
+        <v>16000</v>
       </c>
       <c r="G14" s="6">
         <f>D14*F14</f>
@@ -928,14 +936,10 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>8532354386</t>
-        </is>
-      </c>
+          <t>소망트레이딩</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -943,12 +947,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>NBR 고무 호스</t>
+          <t>연마봉(강철 축) 짧은 것</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>안지름 5 × 바깥지름 10</t>
+          <t>Ø12, 55mm 이상 (55로 절단)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -956,11 +960,11 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>개(약2m)</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>8900</v>
+        <v>1600</v>
       </c>
       <c r="G15" s="6">
         <f>D15*F15</f>
@@ -968,14 +972,10 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>8558801755</t>
-        </is>
-      </c>
+          <t>소망트레이딩</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -983,16 +983,16 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>큰 와셔 DIN9021 M16 (강철)</t>
+          <t>연마봉(변속 레일)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>안지름 17 × 바깥지름 50 × 두께 3</t>
+          <t>Ø6, 371mm</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>710</v>
+        <v>5200</v>
       </c>
       <c r="G16" s="6">
         <f>D16*F16</f>
@@ -1008,14 +1008,10 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>6305734042</t>
-        </is>
-      </c>
+          <t>소망트레이딩</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1023,24 +1019,24 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>코르크 시트</t>
+          <t>6001ZZ 볼 베어링 (10개 묶음)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>두께 2mm, A4</t>
+          <t>12×28×8</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>장</t>
+          <t>묶음</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1890</v>
+        <v>6000</v>
       </c>
       <c r="G17" s="6">
         <f>D17*F17</f>
@@ -1053,7 +1049,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>4845669553</t>
+          <t>8630678241</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1059,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>강구</t>
+          <t>6003ZZ 볼 베어링</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Ø6mm 50개</t>
+          <t>17×35×10</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -1076,11 +1072,11 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>봉</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>3500</v>
+        <v>1100</v>
       </c>
       <c r="G18" s="6">
         <f>D18*F18</f>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>9638493021</t>
+          <t>8230435105</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1099,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>샤프트 칼라 (Ø6 축용)</t>
+          <t>강철 평행핀</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>안지름 6.1, 바깥지름 11, 폭 6, 멈춤나사형 (RC 휠 칼라, 10개)</t>
+          <t>Ø5×25</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -1116,11 +1112,11 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>봉(10개)</t>
+          <t>봉(100개)</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>14800</v>
+        <v>27000</v>
       </c>
       <c r="G19" s="6">
         <f>D19*F19</f>
@@ -1133,7 +1129,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>9669133315</t>
+          <t>9743421687</t>
         </is>
       </c>
     </row>
@@ -1143,16 +1139,16 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>강철 평행핀</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>M3×8 (육각 홈붙이, 스텐)</t>
+          <t>Ø5×40</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -1160,7 +1156,7 @@
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>50</v>
+        <v>440</v>
       </c>
       <c r="G20" s="6">
         <f>D20*F20</f>
@@ -1173,7 +1169,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>8532354386</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1179,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>NBR 고무 호스</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>M3×10</t>
+          <t>안지름 5 × 바깥지름 10</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
@@ -1196,11 +1192,11 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>개(약2m)</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>60</v>
+        <v>8900</v>
       </c>
       <c r="G21" s="6">
         <f>D21*F21</f>
@@ -1213,7 +1209,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>8558801755</t>
         </is>
       </c>
     </row>
@@ -1223,16 +1219,16 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>큰 와셔 DIN9021 M16 (강철)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>M3×12</t>
+          <t>안지름 17 × 바깥지름 50 × 두께 3</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -1240,7 +1236,7 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>60</v>
+        <v>710</v>
       </c>
       <c r="G22" s="6">
         <f>D22*F22</f>
@@ -1253,7 +1249,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>6305734042</t>
         </is>
       </c>
     </row>
@@ -1263,24 +1259,24 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>코르크 시트</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>M3×16</t>
+          <t>두께 2mm, A4</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>장</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>100</v>
+        <v>1890</v>
       </c>
       <c r="G23" s="6">
         <f>D23*F23</f>
@@ -1293,7 +1289,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>4845669553</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1299,24 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 + 너트</t>
+          <t>강구</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>M3×20</t>
+          <t>Ø6mm 50개</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>봉</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>130</v>
+        <v>3500</v>
       </c>
       <c r="G24" s="6">
         <f>D24*F24</f>
@@ -1333,7 +1329,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>9638493021</t>
         </is>
       </c>
     </row>
@@ -1343,24 +1339,24 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>샤프트 칼라 (Ø6 축용)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>M3×25</t>
+          <t>안지름 6.1, 바깥지름 11, 폭 6, 멈춤나사형 (RC 휠 칼라, 10개)</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>봉(10개)</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>70</v>
+        <v>14800</v>
       </c>
       <c r="G25" s="6">
         <f>D25*F25</f>
@@ -1373,7 +1369,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>9669133315</t>
         </is>
       </c>
     </row>
@@ -1388,11 +1384,11 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>M3×50</t>
+          <t>M3×8 (육각 홈붙이, 스텐)</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -1400,7 +1396,7 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="G26" s="6">
         <f>D26*F26</f>
@@ -1423,12 +1419,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>M3 무두볼트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>M3×8</t>
+          <t>M3×10</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
@@ -1453,7 +1449,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>7974822838</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -1463,16 +1459,16 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>M3 평와셔</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>M3 (바깥지름 8, 두께 0.5)</t>
+          <t>M3×12</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -1480,7 +1476,7 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G28" s="6">
         <f>D28*F28</f>
@@ -1493,7 +1489,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>7440529428</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -1503,24 +1499,24 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>M4×16</t>
+          <t>M3×16</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="G29" s="6">
         <f>D29*F29</f>
@@ -1543,16 +1539,16 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M3 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>M4×25</t>
+          <t>M3×20</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -1560,7 +1556,7 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="G30" s="6">
         <f>D30*F30</f>
@@ -1583,24 +1579,24 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>M4×30</t>
+          <t>M3×25</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="G31" s="6">
         <f>D31*F31</f>
@@ -1623,24 +1619,24 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M3 렌치볼트</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>M4×60</t>
+          <t>M3×50</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>350</v>
+        <v>170</v>
       </c>
       <c r="G32" s="6">
         <f>D32*F32</f>
@@ -1663,24 +1659,24 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 너트</t>
+          <t>M3 무두볼트</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>M5×10</t>
+          <t>M3×8</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G33" s="6">
         <f>D33*F33</f>
@@ -1693,7 +1689,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>7974822838</t>
         </is>
       </c>
     </row>
@@ -1703,24 +1699,24 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 너트</t>
+          <t>M3 평와셔</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>M5×20</t>
+          <t>M3 (바깥지름 8, 두께 0.5)</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="G34" s="6">
         <f>D34*F34</f>
@@ -1733,7 +1729,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>6455358137</t>
+          <t>7440529428</t>
         </is>
       </c>
     </row>
@@ -1743,16 +1739,16 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 평와셔</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>M5×8 3개 + M5×12 3개 + M5 와셔 3개</t>
+          <t>M4×16</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -1760,7 +1756,7 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>720</v>
+        <v>170</v>
       </c>
       <c r="G35" s="6">
         <f>D35*F35</f>
@@ -1783,16 +1779,16 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 나일론 너트</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>M5×70</t>
+          <t>M4×25</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -1800,7 +1796,7 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>550</v>
+        <v>160</v>
       </c>
       <c r="G36" s="6">
         <f>D36*F36</f>
@@ -1823,24 +1819,24 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>M6 렌치볼트</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>M6×25</t>
+          <t>M4×30</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="G37" s="6">
         <f>D37*F37</f>
@@ -1863,24 +1859,24 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>M6 너트</t>
+          <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>M6 (맞변 10)</t>
+          <t>M4×60</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G38" s="6">
         <f>D38*F38</f>
@@ -1893,7 +1889,7 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>7687671245</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -1903,24 +1899,24 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>M6 나일론 너트</t>
+          <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>M6 (DIN985, 두께 6)</t>
+          <t>M5×10</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="G39" s="6">
         <f>D39*F39</f>
@@ -1933,7 +1929,7 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>6280971320</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -1943,24 +1939,24 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>목재 나사</t>
+          <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>4×16 둥근머리 1종 (스텐, 26개 봉)</t>
+          <t>M5×20</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>봉(26개)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1150</v>
+        <v>230</v>
       </c>
       <c r="G40" s="6">
         <f>D40*F40</f>
@@ -1973,7 +1969,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>7760964029</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1979,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>에폭시 접착제</t>
+          <t>M5 렌치볼트 + 평와셔</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2액형</t>
+          <t>M5×8 3개 + M5×12 3개 + M5 와셔 3개</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
@@ -1996,11 +1992,11 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>4440</v>
+        <v>720</v>
       </c>
       <c r="G41" s="6">
         <f>D41*F41</f>
@@ -2013,7 +2009,7 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>2725054</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2019,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>순간접착제</t>
+          <t>M5 렌치볼트 + 나일론 너트</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>M5×70</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
@@ -2036,11 +2032,11 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>3000</v>
+        <v>550</v>
       </c>
       <c r="G42" s="6">
         <f>D42*F42</f>
@@ -2053,7 +2049,7 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>8643897709</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -2063,24 +2059,24 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트</t>
+          <t>M6 렌치볼트</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>속선(니플 달린 것) 2m + 아우터 바깥지름 5 2m + 끝 캡</t>
+          <t>M6×25</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>6900</v>
+        <v>210</v>
       </c>
       <c r="G43" s="6">
         <f>D43*F43</f>
@@ -2093,7 +2089,7 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>8305908512</t>
+          <t>6455358137</t>
         </is>
       </c>
     </row>
@@ -2103,24 +2099,24 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>MDF 판</t>
+          <t>M6 너트</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>12T 300×1200 재단</t>
+          <t>M6 (맞변 10)</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>장</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>9600</v>
+        <v>60</v>
       </c>
       <c r="G44" s="6">
         <f>D44*F44</f>
@@ -2133,7 +2129,7 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>71452005</t>
+          <t>7687671245</t>
         </is>
       </c>
     </row>
@@ -2143,24 +2139,24 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>투명 아크릴</t>
+          <t>M6 나일론 너트</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>A3 3T</t>
+          <t>M6 (DIN985, 두께 6)</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>장</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>9000</v>
+        <v>170</v>
       </c>
       <c r="G45" s="6">
         <f>D45*F45</f>
@@ -2173,7 +2169,7 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>9593337115</t>
+          <t>6280971320</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2179,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + 케이블</t>
+          <t>목재 나사</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>ATmega32u4</t>
+          <t>4×16 둥근머리 1종 (스텐, 26개 봉)</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
@@ -2196,11 +2192,11 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>봉(26개)</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>9200</v>
+        <v>1150</v>
       </c>
       <c r="G46" s="6">
         <f>D46*F46</f>
@@ -2213,7 +2209,7 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>1119152790</t>
+          <t>7760964029</t>
         </is>
       </c>
     </row>
@@ -2223,16 +2219,16 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>홀센서 A3144</t>
+          <t>에폭시 접착제</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>3핀 소자</t>
+          <t>2액형</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -2240,7 +2236,7 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>90</v>
+        <v>4440</v>
       </c>
       <c r="G47" s="6">
         <f>D47*F47</f>
@@ -2253,7 +2249,7 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>8520223332</t>
+          <t>2725054</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2259,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>네오디뮴 자석</t>
+          <t>순간접착제</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Ø6×3mm 40개</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
@@ -2276,11 +2272,11 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>봉</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>11300</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="6">
         <f>D48*F48</f>
@@ -2293,7 +2289,7 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>7119515778</t>
+          <t>8643897709</t>
         </is>
       </c>
     </row>
@@ -2303,24 +2299,24 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>마이크로스위치</t>
+          <t>자전거 브레이크 케이블 세트</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>KW-11-3Z 레버형</t>
+          <t>속선(니플 달린 것) 2m + 아우터 바깥지름 5 2m + 끝 캡</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>400</v>
+        <v>6900</v>
       </c>
       <c r="G49" s="6">
         <f>D49*F49</f>
@@ -2333,7 +2329,7 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>9167678186</t>
+          <t>8305908512</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2339,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>점퍼 케이블</t>
+          <t>MDF 판</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>M-F 40P 40cm</t>
+          <t>12T 300×1200 재단</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
@@ -2356,11 +2352,11 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>장</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>5300</v>
+        <v>9600</v>
       </c>
       <c r="G50" s="6">
         <f>D50*F50</f>
@@ -2373,7 +2369,7 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>9699042565</t>
+          <t>71452005</t>
         </is>
       </c>
     </row>
@@ -2383,24 +2379,24 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>만능기판</t>
+          <t>투명 아크릴</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>20개 묶음</t>
+          <t>A3 3T</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>봉</t>
+          <t>장</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="G51" s="6">
         <f>D51*F51</f>
@@ -2413,7 +2409,7 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>9661304796</t>
+          <t>9593337115</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2419,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>자동차 릴레이 + 소켓</t>
+          <t>아두이노 레오나르도 R3 + 케이블</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>12V, 접점 40A, 4핀</t>
+          <t>ATmega32u4</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
@@ -2440,7 +2436,7 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>3100</v>
+        <v>9200</v>
       </c>
       <c r="G52" s="6">
         <f>D52*F52</f>
@@ -2453,7 +2449,7 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>6667848502</t>
+          <t>1119152790</t>
         </is>
       </c>
     </row>
@@ -2463,24 +2459,24 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더</t>
+          <t>홀센서 A3144</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>15A</t>
+          <t>3핀 소자</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>8900</v>
+        <v>90</v>
       </c>
       <c r="G53" s="6">
         <f>D53*F53</f>
@@ -2493,7 +2489,7 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>9663070188</t>
+          <t>8520223332</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2499,16 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>비상정지 스위치</t>
+          <t>마이크로스위치</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>버섯형, b접점(NC)</t>
+          <t>KW-11-3Z 레버형</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -2520,7 +2516,7 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>7700</v>
+        <v>400</v>
       </c>
       <c r="G54" s="6">
         <f>D54*F54</f>
@@ -2533,7 +2529,7 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>9169963218</t>
+          <t>9167678186</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2539,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈</t>
+          <t>점퍼 케이블</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>1채널</t>
+          <t>M-F 40P 40cm</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
@@ -2560,7 +2556,7 @@
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>990</v>
+        <v>5300</v>
       </c>
       <c r="G55" s="6">
         <f>D55*F55</f>
@@ -2573,7 +2569,7 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>7495734120</t>
+          <t>9699042565</t>
         </is>
       </c>
     </row>
@@ -2583,20 +2579,24 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>다이오드 1N4007</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr"/>
+          <t>자동차 릴레이 + 소켓</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>12V, 접점 40A, 4핀</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>봉(10개)</t>
+          <t>개</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>200</v>
+        <v>3100</v>
       </c>
       <c r="G56" s="6">
         <f>D56*F56</f>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>8324531851</t>
+          <t>6667848502</t>
         </is>
       </c>
     </row>
@@ -2619,24 +2619,24 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>전선</t>
+          <t>블레이드 퓨즈 + 인라인 홀더</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>1.5mm²(16AWG) 이상, 적·흑 각 2m</t>
+          <t>15A</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>세트(1m)</t>
+          <t>세트</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1310</v>
+        <v>8900</v>
       </c>
       <c r="G57" s="6">
         <f>D57*F57</f>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>7225302003</t>
+          <t>9663070188</t>
         </is>
       </c>
     </row>
@@ -2659,24 +2659,24 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>압착 단자 세트</t>
+          <t>전선</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>250 규격(6.3mm) 절연 암 평형 단자 (22~16AWG)</t>
+          <t>1.5mm²(16AWG) 이상, 적·흑 각 2m</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>봉(2개)</t>
+          <t>세트(1m)</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>310</v>
+        <v>1310</v>
       </c>
       <c r="G58" s="6">
         <f>D58*F58</f>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>8667960491</t>
+          <t>7225302003</t>
         </is>
       </c>
     </row>
@@ -2699,24 +2699,24 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>저항</t>
+          <t>압착 단자 세트</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>10kΩ 1개 + 4.7kΩ 1개 (1/4W)</t>
+          <t>250 규격(6.3mm) 절연 암 평형 단자 (22~16AWG)</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>세트</t>
+          <t>봉(2개)</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>830</v>
+        <v>310</v>
       </c>
       <c r="G59" s="6">
         <f>D59*F59</f>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>7503391635</t>
+          <t>8667960491</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>67900</v>
+        <v>53200</v>
       </c>
       <c r="G63" s="6">
         <f>D63*F63</f>

--- a/v4/구매신청_최종.xlsx
+++ b/v4/구매신청_최종.xlsx
@@ -10,7 +10,7 @@
     <sheet name="물품 구입 신청" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'물품 구입 신청'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'물품 구입 신청'!$A$1:$I$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>걸이 저울</t>
+          <t>디지털 캘리퍼스</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>0~5kg, 10g 단위</t>
+          <t>0.01mm 표시, 150mm</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>13550</v>
+        <v>7000</v>
       </c>
       <c r="G61" s="6">
         <f>D61*F61</f>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>9619089050</t>
+          <t>8301956558</t>
         </is>
       </c>
     </row>
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스</t>
+          <t>배송비</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>0.01mm 표시, 150mm</t>
+          <t>새 판매처 포함</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
@@ -2832,11 +2832,11 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>식</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>7000</v>
+        <v>53200</v>
       </c>
       <c r="G62" s="6">
         <f>D62*F62</f>
@@ -2844,94 +2844,54 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>8301956558</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>배송비</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>새 판매처 포함</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>식</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>53200</v>
-      </c>
-      <c r="G63" s="6">
-        <f>D63*F63</f>
-        <v/>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>축 양면 D컷 가공 (입력축 435, 출력축 358)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>면 사이 10.0, 전체 길이</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>견적 후</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>가공 업체</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>축 양면 D컷 가공 (입력축 435, 출력축 358)</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>면 사이 10.0, 전체 길이</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>견적 후</t>
-        </is>
-      </c>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>가공 업체</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="n"/>
-    </row>
-    <row r="65">
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="G65" s="11">
-        <f>SUM(G5:G64)</f>
+      <c r="G64" s="11">
+        <f>SUM(G5:G63)</f>
         <v/>
       </c>
     </row>
@@ -2994,7 +2954,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/v4/구매신청_최종.xlsx
+++ b/v4/구매신청_최종.xlsx
@@ -10,7 +10,7 @@
     <sheet name="물품 구입 신청" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'물품 구입 신청'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'물품 구입 신청'!$A$1:$I$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2739,24 +2739,24 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>PLA 필라멘트</t>
+          <t>배송비</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>2.85mm, 1kg 롤</t>
+          <t>새 판매처 포함</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>롤</t>
+          <t>식</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>30600</v>
+        <v>53200</v>
       </c>
       <c r="G60" s="6">
         <f>D60*F60</f>
@@ -2764,134 +2764,54 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>9496076712</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>디지털 캘리퍼스</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>0.01mm 표시, 150mm</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G61" s="6">
-        <f>D61*F61</f>
-        <v/>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>8301956558</t>
-        </is>
-      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>축 양면 D컷 가공 (입력축 435, 출력축 358)</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>면 사이 10.0, 전체 길이</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>견적 후</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>가공 업체</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>배송비</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>새 판매처 포함</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>식</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>53200</v>
-      </c>
-      <c r="G62" s="6">
-        <f>D62*F62</f>
-        <v/>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>축 양면 D컷 가공 (입력축 435, 출력축 358)</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>면 사이 10.0, 전체 길이</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>견적 후</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>가공 업체</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="n"/>
-    </row>
-    <row r="64">
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="G64" s="11">
-        <f>SUM(G5:G63)</f>
+      <c r="G62" s="11">
+        <f>SUM(G5:G61)</f>
         <v/>
       </c>
     </row>
@@ -2952,8 +2872,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/v4/구매신청_최종.xlsx
+++ b/v4/구매신청_최종.xlsx
@@ -2799,7 +2799,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>가공 업체</t>
+          <t>소망트레이딩(가공)</t>
         </is>
       </c>
       <c r="I61" s="9" t="n"/>

--- a/v4/구매신청_최종.xlsx
+++ b/v4/구매신청_최종.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="물품 구입 신청" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="구입처 링크" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'물품 구입 신청'!$A$1:$I$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'물품 구입 신청'!$A$1:$I$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,18 +30,24 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="8"/>
     </font>
     <font>
       <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -66,49 +73,59 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00808080"/>
       </left>
       <right style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00808080"/>
       </right>
       <top style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00808080"/>
       </top>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="00808080"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,2406 +491,3757 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>동아리 학술제 물품 구입 신청(1차) · RPM · 3D프린팅 5단+후진 수동변속기 제작 재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>단가는 2026-10-20 판매처 화면 기준(VAT 포함). 입력축·출력축 양면 D컷 가공비는 별도(가공 업체 견적 후 확정).</t>
-        </is>
-      </c>
+          <t>2026학년도 동아리 학술제 물품 구입 신청서 (1차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>동아리명</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>지도교사</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>홍경표, 장수빈</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>신청일</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026년 10월    일</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>학술제 주제</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>직접 설계·3D 프린팅한 5단+후진 수동변속기로 탐구하는 기어비와 동력 전달 (전시·체험)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>구입 목적</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>수동변속기 제작 재료: 축·베어링·볼트 등 금속 부품, 스프링, 전기·안전 부품 (3D 프린팅 필라멘트는 별도 준비)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>품명</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>구입처</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>상품번호</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
+    <row r="10">
+      <c r="A10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>압축 스프링 C252</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>외경 18, 자유장 32</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>외경 18, 자유장 32, SUS304</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F10" s="8" t="n">
         <v>8360</v>
       </c>
-      <c r="G5" s="6">
-        <f>D5*F5</f>
-        <v/>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G10" s="8">
+        <f>D10*F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>15336269</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
+    <row r="11">
+      <c r="A11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>압축 스프링 C147</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>외경 5, 길이 10</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F11" s="8" t="n">
         <v>990</v>
       </c>
-      <c r="G6" s="6">
-        <f>D6*F6</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G11" s="8">
+        <f>D11*F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>15336164</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
+    <row r="12">
+      <c r="A12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>네오디뮴 자석</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Ø6×3mm</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F12" s="8" t="n">
         <v>220</v>
       </c>
-      <c r="G7" s="6">
-        <f>D7*F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G12" s="8">
+        <f>D12*F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>31671</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+    <row r="13">
+      <c r="A13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>가변저항 B10K</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>회전형 16mm, 축 Ø6 반달(D컷, 평면까지 4.5~4.6), 축 길이 15mm(장착면부터), 부싱 M7</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>16mm, D축 Ø6 15mm, 부싱 M7 (P160KNP-1FD15B10K)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F13" s="8" t="n">
         <v>3993</v>
       </c>
-      <c r="G8" s="6">
-        <f>D8*F8</f>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="G13" s="8">
+        <f>D13*F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>16130996</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="14">
+      <c r="A14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>만능기판</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>하프 사이즈 89×52 (브레드보드형, 양면)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>장</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F14" s="8" t="n">
         <v>2420</v>
       </c>
-      <c r="G9" s="6">
-        <f>D9*F9</f>
-        <v/>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="G14" s="8">
+        <f>D14*F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>12506669</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+    <row r="15">
+      <c r="A15" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>비상정지 스위치</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>버섯형, b접점(NC)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F15" s="8" t="n">
         <v>7370</v>
       </c>
-      <c r="G10" s="6">
-        <f>D10*F10</f>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G15" s="8">
+        <f>D15*F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>10895020</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="16">
+      <c r="A16" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>5V 릴레이 모듈</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>1채널, 로우 트리거</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F16" s="8" t="n">
         <v>990</v>
       </c>
-      <c r="G11" s="6">
-        <f>D11*F11</f>
-        <v/>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="G16" s="8">
+        <f>D16*F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>1327543</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+    <row r="17">
+      <c r="A17" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>다이오드 1N4007</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="4" t="n">
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F17" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="G12" s="6">
-        <f>D12*F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="G17" s="8">
+        <f>D17*F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>3011</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="18">
+      <c r="A18" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>저항</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>10kΩ 30개 + 4.7kΩ 30개 (1/4W, 최소 수량)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F18" s="8" t="n">
         <v>1518</v>
       </c>
-      <c r="G13" s="6">
-        <f>D13*F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="G18" s="8">
+        <f>D18*F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>디바이스마트</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>856</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
+    <row r="19">
+      <c r="A19" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>연마봉(강철 축)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Ø12 1m (435·358·160 으로 절단)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F19" s="8" t="n">
         <v>16000</v>
       </c>
-      <c r="G14" s="6">
-        <f>D14*F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="G19" s="8">
+        <f>D19*F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>소망트레이딩</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="I19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>연마봉(강철 축) 짧은 것</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Ø12, 55mm 이상 (55로 절단)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F20" s="8" t="n">
         <v>1600</v>
       </c>
-      <c r="G15" s="6">
-        <f>D15*F15</f>
-        <v/>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="G20" s="8">
+        <f>D20*F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>소망트레이딩</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="I20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>연마봉(변속 레일)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Ø6, 371mm</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D21" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F21" s="8" t="n">
         <v>5200</v>
       </c>
-      <c r="G16" s="6">
-        <f>D16*F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="G21" s="8">
+        <f>D21*F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>소망트레이딩</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="I21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>6001ZZ 볼 베어링 (10개 묶음)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>12×28×8</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>묶음</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F22" s="8" t="n">
         <v>6000</v>
       </c>
-      <c r="G17" s="6">
-        <f>D17*F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="G22" s="8">
+        <f>D22*F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>8630678241</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
+    <row r="23">
+      <c r="A23" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>6003ZZ 볼 베어링</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>17×35×10</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F23" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="G18" s="6">
-        <f>D18*F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="G23" s="8">
+        <f>D23*F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>8230435105</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="24">
+      <c r="A24" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>강철 평행핀</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Ø5×25</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>봉(100개)</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F24" s="8" t="n">
         <v>27000</v>
       </c>
-      <c r="G19" s="6">
-        <f>D19*F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="G24" s="8">
+        <f>D24*F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>9743421687</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
+    <row r="25">
+      <c r="A25" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>강철 평행핀</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Ø5×40</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D25" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F25" s="8" t="n">
         <v>440</v>
       </c>
-      <c r="G20" s="6">
-        <f>D20*F20</f>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="G25" s="8">
+        <f>D25*F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>8532354386</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="26">
+      <c r="A26" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>NBR 고무 호스</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>안지름 5 × 바깥지름 10</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>개(약2m)</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F26" s="8" t="n">
         <v>8900</v>
       </c>
-      <c r="G21" s="6">
-        <f>D21*F21</f>
-        <v/>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="G26" s="8">
+        <f>D26*F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>8558801755</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
+    <row r="27">
+      <c r="A27" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>큰 와셔 DIN9021 M16 (강철)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>안지름 17 × 바깥지름 50 × 두께 3</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F27" s="8" t="n">
         <v>710</v>
       </c>
-      <c r="G22" s="6">
-        <f>D22*F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="G27" s="8">
+        <f>D27*F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>6305734042</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+    <row r="28">
+      <c r="A28" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>코르크 시트</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>두께 2mm, A4</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>장</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F28" s="8" t="n">
         <v>1890</v>
       </c>
-      <c r="G23" s="6">
-        <f>D23*F23</f>
-        <v/>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="G28" s="8">
+        <f>D28*F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>4845669553</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
+    <row r="29">
+      <c r="A29" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>강구</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Ø6mm 50개</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>봉</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F29" s="8" t="n">
         <v>3500</v>
       </c>
-      <c r="G24" s="6">
-        <f>D24*F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="G29" s="8">
+        <f>D29*F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>9638493021</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+    <row r="30">
+      <c r="A30" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>샤프트 칼라 (Ø6 축용)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>안지름 6.1, 바깥지름 11, 폭 6, 멈춤나사형 (RC 휠 칼라, 10개)</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>봉(10개)</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F30" s="8" t="n">
         <v>14800</v>
       </c>
-      <c r="G25" s="6">
-        <f>D25*F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="G30" s="8">
+        <f>D30*F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>9669133315</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
+    <row r="31">
+      <c r="A31" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>M3×8 (육각 홈붙이, 스텐)</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D31" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F31" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G26" s="6">
-        <f>D26*F26</f>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="G31" s="8">
+        <f>D31*F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
+    <row r="32">
+      <c r="A32" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>M3×10</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F32" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G27" s="6">
-        <f>D27*F27</f>
-        <v/>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="G32" s="8">
+        <f>D32*F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
+    <row r="33">
+      <c r="A33" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>M3×12</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D33" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F33" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G28" s="6">
-        <f>D28*F28</f>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="G33" s="8">
+        <f>D33*F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
+    <row r="34">
+      <c r="A34" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>M3×16</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D34" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F34" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G29" s="6">
-        <f>D29*F29</f>
-        <v/>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="G34" s="8">
+        <f>D34*F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
+    <row r="35">
+      <c r="A35" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>M3 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>M3×20</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D35" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F35" s="8" t="n">
         <v>130</v>
       </c>
-      <c r="G30" s="6">
-        <f>D30*F30</f>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="G35" s="8">
+        <f>D35*F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
+    <row r="36">
+      <c r="A36" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>M3×25</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D36" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F36" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="G31" s="6">
-        <f>D31*F31</f>
-        <v/>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="G36" s="8">
+        <f>D36*F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
+    <row r="37">
+      <c r="A37" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>M3 렌치볼트</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>M3×50</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D37" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F37" s="8" t="n">
         <v>170</v>
       </c>
-      <c r="G32" s="6">
-        <f>D32*F32</f>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="G37" s="8">
+        <f>D37*F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
+    <row r="38">
+      <c r="A38" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>M3 무두볼트</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>M3×8</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F38" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G33" s="6">
-        <f>D33*F33</f>
-        <v/>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="G38" s="8">
+        <f>D38*F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>7974822838</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
+    <row r="39">
+      <c r="A39" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>M3 평와셔</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>M3 (바깥지름 8, 두께 0.5)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D39" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F39" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G34" s="6">
-        <f>D34*F34</f>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="G39" s="8">
+        <f>D39*F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>7440529428</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
+    <row r="40">
+      <c r="A40" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>M4×16</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D40" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F40" s="8" t="n">
         <v>170</v>
       </c>
-      <c r="G35" s="6">
-        <f>D35*F35</f>
-        <v/>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="G40" s="8">
+        <f>D40*F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
+    <row r="41">
+      <c r="A41" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>M4×25</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D41" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F41" s="8" t="n">
         <v>160</v>
       </c>
-      <c r="G36" s="6">
-        <f>D36*F36</f>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="G41" s="8">
+        <f>D41*F41</f>
+        <v/>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
+    <row r="42">
+      <c r="A42" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>M4×30</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D42" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F42" s="8" t="n">
         <v>190</v>
       </c>
-      <c r="G37" s="6">
-        <f>D37*F37</f>
-        <v/>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="G42" s="8">
+        <f>D42*F42</f>
+        <v/>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
+    <row r="43">
+      <c r="A43" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>M4 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>M4×60</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D43" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F43" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="G38" s="6">
-        <f>D38*F38</f>
-        <v/>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="G43" s="8">
+        <f>D43*F43</f>
+        <v/>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
+    <row r="44">
+      <c r="A44" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>M5×10</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D44" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F44" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="G39" s="6">
-        <f>D39*F39</f>
-        <v/>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="G44" s="8">
+        <f>D44*F44</f>
+        <v/>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
+    <row r="45">
+      <c r="A45" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>M5 렌치볼트 + 너트</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>M5×20</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D45" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F45" s="8" t="n">
         <v>230</v>
       </c>
-      <c r="G40" s="6">
-        <f>D40*F40</f>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="G45" s="8">
+        <f>D45*F45</f>
+        <v/>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
+    <row r="46">
+      <c r="A46" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>M5 렌치볼트 + 평와셔</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>M5×8 3개 + M5×12 3개 + M5 와셔 3개</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D46" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F46" s="8" t="n">
         <v>720</v>
       </c>
-      <c r="G41" s="6">
-        <f>D41*F41</f>
-        <v/>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="G46" s="8">
+        <f>D46*F46</f>
+        <v/>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
+    <row r="47">
+      <c r="A47" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>M5 렌치볼트 + 나일론 너트</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>M5×70</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D47" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F47" s="8" t="n">
         <v>550</v>
       </c>
-      <c r="G42" s="6">
-        <f>D42*F42</f>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="G47" s="8">
+        <f>D47*F47</f>
+        <v/>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
+    <row r="48">
+      <c r="A48" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>M6 렌치볼트</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>M6×25</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D48" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F48" s="8" t="n">
         <v>210</v>
       </c>
-      <c r="G43" s="6">
-        <f>D43*F43</f>
-        <v/>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="G48" s="8">
+        <f>D48*F48</f>
+        <v/>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>6455358137</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
+    <row r="49">
+      <c r="A49" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>M6 너트</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>M6 (맞변 10)</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D49" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F49" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G44" s="6">
-        <f>D44*F44</f>
-        <v/>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="G49" s="8">
+        <f>D49*F49</f>
+        <v/>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>7687671245</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
+    <row r="50">
+      <c r="A50" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>M6 나일론 너트</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>M6 (DIN985, 두께 6)</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D50" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F50" s="8" t="n">
         <v>170</v>
       </c>
-      <c r="G45" s="6">
-        <f>D45*F45</f>
-        <v/>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="G50" s="8">
+        <f>D50*F50</f>
+        <v/>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>6280971320</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
+    <row r="51">
+      <c r="A51" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>목재 나사</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>4×16 둥근머리 1종 (스텐, 26개 봉)</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>봉(26개)</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F51" s="8" t="n">
         <v>1150</v>
       </c>
-      <c r="G46" s="6">
-        <f>D46*F46</f>
-        <v/>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="G51" s="8">
+        <f>D51*F51</f>
+        <v/>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>7760964029</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
+    <row r="52">
+      <c r="A52" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>에폭시 접착제</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>2액형</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D52" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F52" s="8" t="n">
         <v>4440</v>
       </c>
-      <c r="G47" s="6">
-        <f>D47*F47</f>
-        <v/>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="G52" s="8">
+        <f>D52*F52</f>
+        <v/>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>2725054</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
+    <row r="53">
+      <c r="A53" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>순간접착제</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D53" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F53" s="8" t="n">
         <v>3000</v>
       </c>
-      <c r="G48" s="6">
-        <f>D48*F48</f>
-        <v/>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="G53" s="8">
+        <f>D53*F53</f>
+        <v/>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>8643897709</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
+    <row r="54">
+      <c r="A54" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>자전거 브레이크 케이블 세트</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>속선(니플 달린 것) 2m + 아우터 바깥지름 5 2m + 끝 캡</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D54" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F54" s="8" t="n">
         <v>6900</v>
       </c>
-      <c r="G49" s="6">
-        <f>D49*F49</f>
-        <v/>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="G54" s="8">
+        <f>D54*F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>8305908512</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
+    <row r="55">
+      <c r="A55" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>MDF 판</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>12T 300×1200 재단</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D55" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>장</t>
         </is>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F55" s="8" t="n">
         <v>9600</v>
       </c>
-      <c r="G50" s="6">
-        <f>D50*F50</f>
-        <v/>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="G55" s="8">
+        <f>D55*F55</f>
+        <v/>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
         <is>
           <t>71452005</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
+    <row r="56">
+      <c r="A56" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>투명 아크릴</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>A3 3T</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D56" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>장</t>
         </is>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F56" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="G51" s="6">
-        <f>D51*F51</f>
-        <v/>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="G56" s="8">
+        <f>D56*F56</f>
+        <v/>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
         <is>
           <t>9593337115</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
+    <row r="57">
+      <c r="A57" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>아두이노 레오나르도 R3 + 케이블</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>ATmega32u4</t>
         </is>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D57" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F57" s="8" t="n">
         <v>9200</v>
       </c>
-      <c r="G52" s="6">
-        <f>D52*F52</f>
-        <v/>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="G57" s="8">
+        <f>D57*F57</f>
+        <v/>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
         <is>
           <t>1119152790</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
+    <row r="58">
+      <c r="A58" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>홀센서 A3144</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>3핀 소자</t>
         </is>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D58" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F58" s="8" t="n">
         <v>90</v>
       </c>
-      <c r="G53" s="6">
-        <f>D53*F53</f>
-        <v/>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="G58" s="8">
+        <f>D58*F58</f>
+        <v/>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
         <is>
           <t>8520223332</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
+    <row r="59">
+      <c r="A59" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>마이크로스위치</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>KW-11-3Z 레버형</t>
         </is>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D59" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F59" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="G54" s="6">
-        <f>D54*F54</f>
-        <v/>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="G59" s="8">
+        <f>D59*F59</f>
+        <v/>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
         <is>
           <t>9167678186</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
+    <row r="60">
+      <c r="A60" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>점퍼 케이블</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>M-F 40P 40cm</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="F60" s="8" t="n">
         <v>5300</v>
       </c>
-      <c r="G55" s="6">
-        <f>D55*F55</f>
-        <v/>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="G60" s="8">
+        <f>D60*F60</f>
+        <v/>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
         <is>
           <t>9699042565</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="n">
+    <row r="61">
+      <c r="A61" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>자동차 릴레이 + 소켓</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>12V, 접점 40A, 4핀</t>
         </is>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D61" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F61" s="8" t="n">
         <v>3100</v>
       </c>
-      <c r="G56" s="6">
-        <f>D56*F56</f>
-        <v/>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="G61" s="8">
+        <f>D61*F61</f>
+        <v/>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
         <is>
           <t>6667848502</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
+    <row r="62">
+      <c r="A62" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>블레이드 퓨즈 + 인라인 홀더</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>15A</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D62" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>세트</t>
         </is>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F62" s="8" t="n">
         <v>8900</v>
       </c>
-      <c r="G57" s="6">
-        <f>D57*F57</f>
-        <v/>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="G62" s="8">
+        <f>D62*F62</f>
+        <v/>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
         <is>
           <t>9663070188</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
+    <row r="63">
+      <c r="A63" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>전선</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>1.5mm²(16AWG) 이상, 적·흑 각 2m</t>
         </is>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D63" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>세트(1m)</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F63" s="8" t="n">
         <v>1310</v>
       </c>
-      <c r="G58" s="6">
-        <f>D58*F58</f>
-        <v/>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="G63" s="8">
+        <f>D63*F63</f>
+        <v/>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>7225302003</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
+    <row r="64">
+      <c r="A64" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>압착 단자 세트</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>250 규격(6.3mm) 절연 암 평형 단자 (22~16AWG)</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D64" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>봉(2개)</t>
         </is>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F64" s="8" t="n">
         <v>310</v>
       </c>
-      <c r="G59" s="6">
-        <f>D59*F59</f>
-        <v/>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="G64" s="8">
+        <f>D64*F64</f>
+        <v/>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
         <is>
           <t>8667960491</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
+    <row r="65">
+      <c r="A65" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>배송비</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>새 판매처 포함</t>
         </is>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>식</t>
         </is>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F65" s="8" t="n">
         <v>53200</v>
       </c>
-      <c r="G60" s="6">
-        <f>D60*F60</f>
-        <v/>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="G65" s="8">
+        <f>D65*F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="n">
+      <c r="I65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>축 양면 D컷 가공 (입력축 435, 출력축 358)</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>면 사이 10.0, 전체 길이</t>
         </is>
       </c>
-      <c r="D61" s="8" t="n">
+      <c r="D66" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="F66" s="11" t="n"/>
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>견적 후</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>소망트레이딩(가공)</t>
         </is>
       </c>
-      <c r="I61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="G62" s="11">
-        <f>SUM(G5:G61)</f>
-        <v/>
+      <c r="I66" s="11" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>합계 (가공비 제외)</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="12">
+        <f>SUM(G10:G66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>※ 단가는 2026-10-20 판매처 화면 가격(VAT 포함)이며 주문 시점에 조금 달라질 수 있음. 배송비는 판매처별 합계. 축 양면 D컷 가공비는 소망트레이딩 견적 회신 후 확정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>신청자:</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                (서명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>지도교사:</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                (서명)</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C5:I5"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId55"/>
   </hyperlinks>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>구입처</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>상품 링크</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>압축 스프링 C252</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=15336269</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>압축 스프링 C147</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=15336164</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>네오디뮴 자석</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=31671</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>가변저항 B10K</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=16130996</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>만능기판</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=12506669</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>비상정지 스위치</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=10895020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5V 릴레이 모듈</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=1327543</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>다이오드 1N4007</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>저항</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>디바이스마트</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.devicemart.co.kr/goods/view?no=856</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>연마봉(강철 축)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>소망트레이딩</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://smball.co.kr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>연마봉(강철 축) 짧은 것</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>소망트레이딩</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://smball.co.kr/product/detail.html?product_no=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>연마봉(변속 레일)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>소망트레이딩</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://smball.co.kr/product/detail.html?product_no=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6001ZZ 볼 베어링 (10개 묶음)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8630678241</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6003ZZ 볼 베어링</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8230435105</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>강철 평행핀</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9743421687</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>강철 평행핀</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8532354386</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NBR 고무 호스</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8558801755</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>큰 와셔 DIN9021 M16 (강철)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6305734042</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>코르크 시트</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/4845669553</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>강구</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9638493021</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>샤프트 칼라 (Ø6 축용)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9669133315</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M3 렌치볼트</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M3 렌치볼트</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M3 렌치볼트</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M3 렌치볼트</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M3 렌치볼트 + 너트</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M3 렌치볼트</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M3 렌치볼트</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M3 무두볼트</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7974822838</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M3 평와셔</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M4 렌치볼트 + 너트</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M4 렌치볼트 + 너트</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M4 렌치볼트 + 너트</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M4 렌치볼트 + 너트</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M5 렌치볼트 + 너트</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M5 렌치볼트 + 너트</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M5 렌치볼트 + 평와셔</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M5 렌치볼트 + 나일론 너트</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M6 렌치볼트</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M6 너트</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7687671245</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M6 나일론 너트</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6280971320</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>목재 나사</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7760964029</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>에폭시 접착제</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/2725054</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>순간접착제</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8643897709</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>자전거 브레이크 케이블 세트</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8305908512</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MDF 판</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/71452005</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>투명 아크릴</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9593337115</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>아두이노 레오나르도 R3 + 케이블</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1119152790</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>홀센서 A3144</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8520223332</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>마이크로스위치</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9167678186</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>점퍼 케이블</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9699042565</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>자동차 릴레이 + 소켓</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6667848502</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>블레이드 퓨즈 + 인라인 홀더</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9663070188</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>전선</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7225302003</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>압착 단자 세트</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>쿠팡</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8667960491</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>배송비</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/v4/구매신청_최종.xlsx
+++ b/v4/구매신청_최종.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="물품 구입 신청" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="구입처 링크" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물품 구입 신청" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구입처 링크" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'물품 구입 신청'!$A$1:$I$71</definedName>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
